--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>图片</t>
   </si>
@@ -212,6 +212,9 @@
     <t>报关产品属性</t>
   </si>
   <si>
+    <t>保险属性</t>
+  </si>
+  <si>
     <t>报关申报价（$）</t>
   </si>
   <si>
@@ -456,6 +459,9 @@
   </si>
   <si>
     <t>{.productProperty}</t>
+  </si>
+  <si>
+    <t>{.insuranceProperty}</t>
   </si>
   <si>
     <t>{.declarePrice}</t>
@@ -1008,7 +1014,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1696,14 +1702,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CD2"/>
+  <dimension ref="A1:CE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="82" width="16" customWidth="1"/>
+    <col min="2" max="61" width="16" customWidth="1"/>
+    <col min="62" max="62" width="15.75" customWidth="1"/>
+    <col min="63" max="83" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:82">
+    <row r="1" customFormat="1" spans="1:83">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1950,253 +1958,259 @@
       <c r="CD1" t="s">
         <v>81</v>
       </c>
+      <c r="CE1" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="2" spans="1:82">
+    <row r="2" spans="1:83">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="CE2" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t>图片</t>
   </si>
@@ -35,6 +35,12 @@
     <t>spuNo</t>
   </si>
   <si>
+    <t>款名（中文）</t>
+  </si>
+  <si>
+    <t>款名（英文）</t>
+  </si>
+  <si>
     <t>sku编号</t>
   </si>
   <si>
@@ -282,6 +288,12 @@
   </si>
   <si>
     <t>{.spuNo}</t>
+  </si>
+  <si>
+    <t>{.productModelName}</t>
+  </si>
+  <si>
+    <t>{.productModelNameEn}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1702,16 +1714,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CE2"/>
+  <dimension ref="A1:CG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="61" width="16" customWidth="1"/>
-    <col min="62" max="62" width="15.75" customWidth="1"/>
-    <col min="63" max="83" width="16" customWidth="1"/>
+    <col min="2" max="63" width="16" customWidth="1"/>
+    <col min="64" max="64" width="15.75" customWidth="1"/>
+    <col min="65" max="85" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:83">
+    <row r="1" customFormat="1" spans="1:85">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1961,256 +1973,268 @@
       <c r="CE1" t="s">
         <v>82</v>
       </c>
+      <c r="CF1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="2" spans="1:83">
+    <row r="2" spans="1:85">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
+      </c>
+      <c r="CF2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="CG2" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -290,10 +290,10 @@
     <t>{.spuNo}</t>
   </si>
   <si>
-    <t>{.productModelName}</t>
-  </si>
-  <si>
-    <t>{.productModelNameEn}</t>
+    <t>{.spuName}</t>
+  </si>
+  <si>
+    <t>{.spuNameEn}</t>
   </si>
   <si>
     <t>{.skuNo}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -248,34 +248,34 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)</t>
-  </si>
-  <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
-  </si>
-  <si>
-    <t>毛重</t>
-  </si>
-  <si>
-    <t>净重</t>
-  </si>
-  <si>
-    <t>单箱重量</t>
-  </si>
-  <si>
-    <t>单箱数量</t>
+    <t>产品尺寸(长，cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽，cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高，cm)</t>
+  </si>
+  <si>
+    <t>箱规(长，cm)</t>
+  </si>
+  <si>
+    <t>箱规(宽，cm)</t>
+  </si>
+  <si>
+    <t>箱规(高，cm)</t>
+  </si>
+  <si>
+    <t>毛重(g)</t>
+  </si>
+  <si>
+    <t>净重(g)</t>
+  </si>
+  <si>
+    <t>单箱重量(kg)</t>
+  </si>
+  <si>
+    <t>单箱数量(kg)</t>
   </si>
   <si>
     <t>推荐仓位(小货区)</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -248,22 +248,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长，cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽，cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高，cm)</t>
-  </si>
-  <si>
-    <t>箱规(长，cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽，cm)</t>
-  </si>
-  <si>
-    <t>箱规(高，cm)</t>
+    <t>产品尺寸(长，mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽，mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高，mm)</t>
+  </si>
+  <si>
+    <t>箱规(长，mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽，mm)</t>
+  </si>
+  <si>
+    <t>箱规(高，mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>
@@ -275,7 +275,7 @@
     <t>单箱重量(kg)</t>
   </si>
   <si>
-    <t>单箱数量(kg)</t>
+    <t>单箱数量(个)</t>
   </si>
   <si>
     <t>推荐仓位(小货区)</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="产品sku明细表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>图片</t>
   </si>
@@ -74,6 +74,9 @@
     <t>品牌</t>
   </si>
   <si>
+    <t>研发团队</t>
+  </si>
+  <si>
     <t>产品开发状态</t>
   </si>
   <si>
@@ -327,6 +330,9 @@
   </si>
   <si>
     <t>{.brandName}</t>
+  </si>
+  <si>
+    <t>{.rdtTeamName}</t>
   </si>
   <si>
     <t>{.productStateName}</t>
@@ -1714,16 +1720,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CG2"/>
+  <dimension ref="A1:CH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="63" width="16" customWidth="1"/>
-    <col min="64" max="64" width="15.75" customWidth="1"/>
-    <col min="65" max="85" width="16" customWidth="1"/>
+    <col min="2" max="64" width="16" customWidth="1"/>
+    <col min="65" max="65" width="15.75" customWidth="1"/>
+    <col min="66" max="86" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:85">
+    <row r="1" customFormat="1" spans="1:86">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1979,262 +1985,268 @@
       <c r="CG1" t="s">
         <v>84</v>
       </c>
+      <c r="CH1" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="2" spans="1:85">
+    <row r="2" spans="1:86">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="CH2" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="产品sku明细表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t>图片</t>
   </si>
@@ -224,6 +224,9 @@
     <t>保险属性</t>
   </si>
   <si>
+    <t>电池重量（g）</t>
+  </si>
+  <si>
     <t>报关申报价（$）</t>
   </si>
   <si>
@@ -480,6 +483,9 @@
   </si>
   <si>
     <t>{.insuranceProperty}</t>
+  </si>
+  <si>
+    <t>{.batteryWeight}</t>
   </si>
   <si>
     <t>{.declarePrice}</t>
@@ -1720,16 +1726,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CH2"/>
+  <dimension ref="A1:CI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="64" width="16" customWidth="1"/>
     <col min="65" max="65" width="15.75" customWidth="1"/>
-    <col min="66" max="86" width="16" customWidth="1"/>
+    <col min="66" max="87" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:86">
+    <row r="1" customFormat="1" spans="1:87">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1988,265 +1994,271 @@
       <c r="CH1" t="s">
         <v>85</v>
       </c>
+      <c r="CI1" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:87">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BT2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CB2" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="CC2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CD2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CG2" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="CI2" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -74,7 +74,7 @@
     <t>品牌</t>
   </si>
   <si>
-    <t>研发团队</t>
+    <t>研发团队（产线）</t>
   </si>
   <si>
     <t>产品开发状态</t>
@@ -1186,8 +1186,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1781,7 +1784,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
@@ -1999,265 +2002,265 @@
       </c>
     </row>
     <row r="2" spans="1:87">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AG2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AH2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AM2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AN2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AO2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AP2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AR2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AS2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AT2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AU2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AV2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AW2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AX2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AY2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BC2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BD2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BE2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BF2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BG2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BH2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BI2" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BK2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BL2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BM2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BN2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BO2" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BP2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BR2" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BS2" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BT2" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="BU2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="BV2" s="1" t="s">
+      <c r="BV2" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BW2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BX2" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="BY2" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CA2" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CB2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="CC2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CD2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CE2" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="CF2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CG2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="CH2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="CI2" s="2" t="s">
         <v>173</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="产品sku明细表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t>图片</t>
   </si>
@@ -77,6 +77,9 @@
     <t>研发团队（产线）</t>
   </si>
   <si>
+    <t>BU线</t>
+  </si>
+  <si>
     <t>产品开发状态</t>
   </si>
   <si>
@@ -336,6 +339,9 @@
   </si>
   <si>
     <t>{.rdtTeamName}</t>
+  </si>
+  <si>
+    <t>{.buName}</t>
   </si>
   <si>
     <t>{.productStateName}</t>
@@ -1729,16 +1735,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="64" width="16" customWidth="1"/>
-    <col min="65" max="65" width="15.75" customWidth="1"/>
-    <col min="66" max="87" width="16" customWidth="1"/>
+    <col min="2" max="65" width="16" customWidth="1"/>
+    <col min="66" max="66" width="15.75" customWidth="1"/>
+    <col min="67" max="88" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:87">
+    <row r="1" customFormat="1" spans="1:88">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2000,268 +2006,274 @@
       <c r="CI1" t="s">
         <v>86</v>
       </c>
+      <c r="CJ1" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="2" spans="1:87">
+    <row r="2" spans="1:88">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+      <c r="CJ2" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="产品sku明细表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t>图片</t>
   </si>
@@ -176,12 +176,6 @@
     <t>首批到货状态</t>
   </si>
   <si>
-    <t>一级供应商</t>
-  </si>
-  <si>
-    <t>二级供应商</t>
-  </si>
-  <si>
     <t>年目标销量</t>
   </si>
   <si>
@@ -438,12 +432,6 @@
   </si>
   <si>
     <t>{.arrivalState}</t>
-  </si>
-  <si>
-    <t>{.mainSupplier}</t>
-  </si>
-  <si>
-    <t>{.secondSupplier}</t>
   </si>
   <si>
     <t>{.yearSaleQty}</t>
@@ -1735,16 +1723,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="65" width="16" customWidth="1"/>
-    <col min="66" max="66" width="15.75" customWidth="1"/>
-    <col min="67" max="88" width="16" customWidth="1"/>
+    <col min="2" max="63" width="16" customWidth="1"/>
+    <col min="64" max="64" width="15.75" customWidth="1"/>
+    <col min="65" max="86" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:88">
+    <row r="1" customFormat="1" spans="1:86">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2003,277 +1991,265 @@
       <c r="CH1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" t="s">
+    </row>
+    <row r="2" spans="1:86">
+      <c r="A2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="2" spans="1:88">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BO2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BP2" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BU2" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BV2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="BU2" s="2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productDetail.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t>图片</t>
   </si>
@@ -74,6 +74,9 @@
     <t>品牌</t>
   </si>
   <si>
+    <t>一级供应商体系认证</t>
+  </si>
+  <si>
     <t>研发团队（产线）</t>
   </si>
   <si>
@@ -330,6 +333,9 @@
   </si>
   <si>
     <t>{.brandName}</t>
+  </si>
+  <si>
+    <t>{.firstCertificateNames}</t>
   </si>
   <si>
     <t>{.rdtTeamName}</t>
@@ -1723,16 +1729,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CH2"/>
+  <dimension ref="A1:CI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="63" width="16" customWidth="1"/>
-    <col min="64" max="64" width="15.75" customWidth="1"/>
-    <col min="65" max="86" width="16" customWidth="1"/>
+    <col min="2" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="21.5" customWidth="1"/>
+    <col min="17" max="64" width="16" customWidth="1"/>
+    <col min="65" max="65" width="15.75" customWidth="1"/>
+    <col min="66" max="87" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:86">
+    <row r="1" customFormat="1" spans="1:87">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1789,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
@@ -1991,265 +1999,271 @@
       <c r="CH1" t="s">
         <v>85</v>
       </c>
+      <c r="CI1" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:87">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
